--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
@@ -4413,7 +4413,7 @@
         <v>1.038188247577402</v>
       </c>
       <c r="D156">
-        <v>0.9851682387696213</v>
+        <v>0.9851682387696212</v>
       </c>
       <c r="E156">
         <v>1.038921105082576</v>
@@ -4439,7 +4439,7 @@
         <v>1.128298400042246</v>
       </c>
       <c r="D157">
-        <v>0.9142749187225783</v>
+        <v>0.9142749187225782</v>
       </c>
       <c r="E157">
         <v>1.12323435138345</v>
@@ -10289,7 +10289,7 @@
         <v>1.122465041793673</v>
       </c>
       <c r="D382">
-        <v>0.6054569678769346</v>
+        <v>0.6054569678769345</v>
       </c>
       <c r="E382">
         <v>1.098995670757197</v>
